--- a/ci-build/CodeSystem-onko-therapy-intent.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:15:17+00:00</t>
+    <t>2026-06-15T08:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-intent.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:40:43+00:00</t>
+    <t>2026-06-15T08:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-intent.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:59:58+00:00</t>
+    <t>2026-06-18T07:59:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-intent.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T07:59:27+00:00</t>
+    <t>2026-06-18T08:40:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-intent.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:58+00:00</t>
+    <t>2026-06-18T08:53:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-intent.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:53:27+00:00</t>
+    <t>2026-06-18T08:56:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-intent.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:56:30+00:00</t>
+    <t>2026-06-18T10:39:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-intent.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T10:39:29+00:00</t>
+    <t>2026-06-18T11:30:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-intent.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T11:30:08+00:00</t>
+    <t>2026-06-23T16:45:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-intent.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T16:45:59+00:00</t>
+    <t>2026-06-24T07:38:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-intent.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T07:38:46+00:00</t>
+    <t>2026-06-25T15:12:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-intent.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:12:52+00:00</t>
+    <t>2026-07-10T09:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-intent.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T09:26:12+00:00</t>
+    <t>2026-07-20T12:02:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
